--- a/Reports/AreDifferent/decryption_coldWater_byHouse2_house/decryption_coldWater_byHouse2_house.xlsx
+++ b/Reports/AreDifferent/decryption_coldWater_byHouse2_house/decryption_coldWater_byHouse2_house.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\AreDifferent\decryption_coldWater_byHouse2_house\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DACF39-90A8-4BBB-8A50-1956146C8597}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="390" windowWidth="28440" windowHeight="12195"/>
+    <workbookView xWindow="180" yWindow="390" windowWidth="28440" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -14,18 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="218">
-  <si>
-    <t>Утверждаю :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">по жилищно-коммунальному хозяйству </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="209">
   <si>
     <t>Справка по расчету субсидий на холодное водоснабжение</t>
-  </si>
-  <si>
-    <t>ООО "ЭнергоКомпания"</t>
   </si>
   <si>
     <t>№ 
@@ -109,21 +106,6 @@
     <t>Баня</t>
   </si>
   <si>
-    <t>Подписи  :</t>
-  </si>
-  <si>
-    <t>Производитель:</t>
-  </si>
-  <si>
-    <t>Служба:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Директор МКУ "СЗ ЖКХ" </t>
-  </si>
-  <si>
-    <t>______________________ Д.В.Игошин</t>
-  </si>
-  <si>
     <t>Нач.ПЭО________________ Л.Д.Сафонова</t>
   </si>
   <si>
@@ -634,55 +616,52 @@
     <t>$t1['noMKD']</t>
   </si>
   <si>
-    <t xml:space="preserve"> ______________ Д.А.Соловьев</t>
-  </si>
-  <si>
     <t>Начальник ПЭО</t>
   </si>
   <si>
-    <t>______________М.Е.Праздников</t>
-  </si>
-  <si>
     <t>"за ".$this-&gt;H['full_name_month']</t>
   </si>
   <si>
     <t>$this-&gt;H['name_organization']</t>
   </si>
   <si>
-    <t>И. о. заместителя Главы Беловского городского округа</t>
-  </si>
-  <si>
-    <t>(на осн.доверенности № 1/6733-8 от 13.12.2024)</t>
-  </si>
-  <si>
-    <t>___________________   Е. Т. Муратов</t>
-  </si>
-  <si>
-    <t>"______"_________________   2025</t>
-  </si>
-  <si>
-    <t>Вед.специалист по ВКХ_______________Н.А.Крюкова</t>
-  </si>
-  <si>
-    <t>Главный инженер</t>
-  </si>
-  <si>
-    <t>__________________ Е. В. Сикова</t>
-  </si>
-  <si>
-    <t>Приложение  к Соглашению № 30-юр  с 29.01.2025</t>
+    <t>Получатель субсидии:</t>
+  </si>
+  <si>
+    <t>Распорядитель субсидии:</t>
+  </si>
+  <si>
+    <t>Начальник УЖКиДК АБГО</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ______________ Соловьев Д.А.</t>
+  </si>
+  <si>
+    <t>Генеральный директор ООО"ЭК"________________ Игошин Д.В.</t>
+  </si>
+  <si>
+    <t>Начальник ПТО</t>
+  </si>
+  <si>
+    <t>______________Кочегаров Д.В.</t>
+  </si>
+  <si>
+    <t>______________Праздников М.Е.</t>
+  </si>
+  <si>
+    <t>Вед.специалист по ВКХ________________ Н.А.Крюкова</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1239,6 +1218,89 @@
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1257,98 +1319,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный_Водичка с 01.05. 2009г" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный_Водичка с 01.05. 2009г" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1638,12 +1625,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BI63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
@@ -1655,24 +1642,24 @@
     <col min="23" max="33" width="9.85546875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="26" customFormat="1">
+    <row r="1" spans="1:38" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AH1" s="26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AI1" s="26" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ1" s="26" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AK1" s="26">
         <v>19</v>
       </c>
       <c r="AL1" s="26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" s="26" customFormat="1" ht="18.75">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="58"/>
       <c r="B2" s="58"/>
       <c r="C2" s="58"/>
@@ -1687,9 +1674,7 @@
       <c r="L2" s="58"/>
       <c r="M2" s="58"/>
       <c r="N2" s="59"/>
-      <c r="O2" s="60" t="s">
-        <v>217</v>
-      </c>
+      <c r="O2" s="60"/>
       <c r="P2" s="59"/>
       <c r="Q2" s="59"/>
       <c r="R2" s="61"/>
@@ -1709,7 +1694,7 @@
       <c r="AF2" s="63"/>
       <c r="AG2" s="63"/>
     </row>
-    <row r="3" spans="1:38" s="26" customFormat="1">
+    <row r="3" spans="1:38" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58"/>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -1744,7 +1729,7 @@
       <c r="AF3" s="58"/>
       <c r="AG3" s="58"/>
     </row>
-    <row r="4" spans="1:38" s="26" customFormat="1" ht="18.75">
+    <row r="4" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="58"/>
       <c r="B4" s="58"/>
       <c r="C4" s="58"/>
@@ -1759,9 +1744,7 @@
       <c r="L4" s="58"/>
       <c r="M4" s="58"/>
       <c r="N4" s="58"/>
-      <c r="O4" s="65" t="s">
-        <v>0</v>
-      </c>
+      <c r="O4" s="65"/>
       <c r="P4" s="58"/>
       <c r="R4" s="31"/>
       <c r="S4" s="31"/>
@@ -1780,7 +1763,7 @@
       <c r="AF4" s="66"/>
       <c r="AG4" s="66"/>
     </row>
-    <row r="5" spans="1:38" s="26" customFormat="1" ht="18.75">
+    <row r="5" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="58"/>
       <c r="B5" s="58"/>
       <c r="C5" s="58"/>
@@ -1795,9 +1778,7 @@
       <c r="L5" s="58"/>
       <c r="M5" s="58"/>
       <c r="N5" s="58"/>
-      <c r="O5" s="65" t="s">
-        <v>210</v>
-      </c>
+      <c r="O5" s="65"/>
       <c r="P5" s="58"/>
       <c r="R5" s="31"/>
       <c r="S5" s="31"/>
@@ -1816,7 +1797,7 @@
       <c r="AF5" s="66"/>
       <c r="AG5" s="66"/>
     </row>
-    <row r="6" spans="1:38" s="26" customFormat="1" ht="18.75">
+    <row r="6" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="58"/>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
@@ -1831,9 +1812,7 @@
       <c r="L6" s="58"/>
       <c r="M6" s="58"/>
       <c r="N6" s="58"/>
-      <c r="O6" s="65" t="s">
-        <v>1</v>
-      </c>
+      <c r="O6" s="65"/>
       <c r="P6" s="58"/>
       <c r="R6" s="31"/>
       <c r="S6" s="31"/>
@@ -1852,7 +1831,7 @@
       <c r="AF6" s="66"/>
       <c r="AG6" s="66"/>
     </row>
-    <row r="7" spans="1:38" s="26" customFormat="1" ht="18.75">
+    <row r="7" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="58"/>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -1867,9 +1846,7 @@
       <c r="L7" s="58"/>
       <c r="M7" s="58"/>
       <c r="N7" s="58"/>
-      <c r="O7" s="65" t="s">
-        <v>211</v>
-      </c>
+      <c r="O7" s="65"/>
       <c r="P7" s="58"/>
       <c r="R7" s="31"/>
       <c r="S7" s="31"/>
@@ -1888,7 +1865,7 @@
       <c r="AF7" s="66"/>
       <c r="AG7" s="66"/>
     </row>
-    <row r="8" spans="1:38" s="26" customFormat="1">
+    <row r="8" spans="1:38" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58"/>
       <c r="B8" s="58"/>
       <c r="C8" s="58"/>
@@ -1922,7 +1899,7 @@
       <c r="AF8" s="66"/>
       <c r="AG8" s="66"/>
     </row>
-    <row r="9" spans="1:38" s="26" customFormat="1" ht="18.75">
+    <row r="9" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="58"/>
       <c r="B9" s="58"/>
       <c r="C9" s="58"/>
@@ -1937,9 +1914,7 @@
       <c r="L9" s="58"/>
       <c r="M9" s="58"/>
       <c r="N9" s="58"/>
-      <c r="O9" s="65" t="s">
-        <v>212</v>
-      </c>
+      <c r="O9" s="65"/>
       <c r="P9" s="58"/>
       <c r="R9" s="31"/>
       <c r="S9" s="31"/>
@@ -1958,7 +1933,7 @@
       <c r="AF9" s="66"/>
       <c r="AG9" s="66"/>
     </row>
-    <row r="10" spans="1:38" s="26" customFormat="1" ht="18.75">
+    <row r="10" spans="1:38" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="58"/>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
@@ -1973,9 +1948,7 @@
       <c r="L10" s="58"/>
       <c r="M10" s="58"/>
       <c r="N10" s="58"/>
-      <c r="O10" s="65" t="s">
-        <v>213</v>
-      </c>
+      <c r="O10" s="65"/>
       <c r="P10" s="58"/>
       <c r="R10" s="68"/>
       <c r="S10" s="68"/>
@@ -1994,7 +1967,7 @@
       <c r="AF10" s="58"/>
       <c r="AG10" s="58"/>
     </row>
-    <row r="11" spans="1:38" s="26" customFormat="1">
+    <row r="11" spans="1:38" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
@@ -2029,7 +2002,7 @@
       <c r="AF11" s="58"/>
       <c r="AG11" s="58"/>
     </row>
-    <row r="12" spans="1:38" s="26" customFormat="1">
+    <row r="12" spans="1:38" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="58"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
@@ -2065,30 +2038,30 @@
       <c r="AG12" s="58"/>
       <c r="AH12" s="31"/>
     </row>
-    <row r="13" spans="1:38" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="85" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="86"/>
-      <c r="N13" s="86"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="86"/>
-      <c r="R13" s="86"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="86"/>
-      <c r="U13" s="86"/>
+    <row r="13" spans="1:38" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="115"/>
+      <c r="M13" s="115"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="115"/>
+      <c r="T13" s="115"/>
+      <c r="U13" s="115"/>
       <c r="V13" s="69"/>
       <c r="W13" s="69"/>
       <c r="X13" s="69"/>
@@ -2102,30 +2075,30 @@
       <c r="AF13" s="69"/>
       <c r="AG13" s="69"/>
     </row>
-    <row r="14" spans="1:38" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="89" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
+    <row r="14" spans="1:38" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="118" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="119"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="119"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="119"/>
+      <c r="R14" s="119"/>
+      <c r="S14" s="119"/>
+      <c r="T14" s="119"/>
+      <c r="U14" s="119"/>
       <c r="V14" s="70"/>
       <c r="W14" s="70"/>
       <c r="X14" s="70"/>
@@ -2139,30 +2112,30 @@
       <c r="AF14" s="70"/>
       <c r="AG14" s="70"/>
     </row>
-    <row r="15" spans="1:38" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A15" s="87" t="s">
-        <v>209</v>
-      </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="88"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="88"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
+    <row r="15" spans="1:38" s="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="116" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
       <c r="V15" s="71"/>
       <c r="W15" s="71"/>
       <c r="X15" s="71"/>
@@ -2176,190 +2149,190 @@
       <c r="AF15" s="71"/>
       <c r="AG15" s="71"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="91" t="s">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="86" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="106"/>
+      <c r="D16" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="99"/>
-      <c r="D16" s="91" t="s">
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91" t="s">
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="86"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="R16" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="91"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="94" t="s">
+      <c r="S16" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="97" t="s">
+      <c r="T16" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="R16" s="98" t="s">
+      <c r="U16" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="S16" s="97" t="s">
+      <c r="V16" s="42"/>
+      <c r="W16" s="87" t="s">
+        <v>162</v>
+      </c>
+      <c r="X16" s="90" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y16" s="91"/>
+      <c r="Z16" s="90" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA16" s="92"/>
+      <c r="AB16" s="93" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC16" s="93" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD16" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE16" s="98"/>
+      <c r="AF16" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG16" s="99"/>
+    </row>
+    <row r="17" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="86"/>
+      <c r="B17" s="86"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="T16" s="98" t="s">
+      <c r="E17" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="U16" s="98" t="s">
+      <c r="F17" s="86"/>
+      <c r="G17" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="V16" s="42"/>
-      <c r="W16" s="113" t="s">
-        <v>170</v>
-      </c>
-      <c r="X16" s="114" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y16" s="115"/>
-      <c r="Z16" s="114" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA16" s="116"/>
-      <c r="AB16" s="117" t="s">
-        <v>173</v>
-      </c>
-      <c r="AC16" s="117" t="s">
-        <v>174</v>
-      </c>
-      <c r="AD16" s="104" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE16" s="105"/>
-      <c r="AF16" s="104" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG16" s="106"/>
-    </row>
-    <row r="17" spans="1:46" ht="15" customHeight="1">
-      <c r="A17" s="91"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="91" t="s">
+      <c r="H17" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91" t="s">
+      <c r="L17" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="91" t="s">
+      <c r="M17" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="94" t="s">
+      <c r="N17" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="L17" s="94" t="s">
+      <c r="O17" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="M17" s="94" t="s">
+      <c r="P17" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="N17" s="94" t="s">
+      <c r="Q17" s="109"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="109"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y17" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z17" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA17" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB17" s="94"/>
+      <c r="AC17" s="94"/>
+      <c r="AD17" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE17" s="101" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF17" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="AG17" s="101" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:46" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="86"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O17" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="94" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" s="97"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="97"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="108"/>
-      <c r="X17" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y17" s="107" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z17" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA17" s="107" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB17" s="118"/>
-      <c r="AC17" s="118"/>
-      <c r="AD17" s="110" t="s">
-        <v>199</v>
-      </c>
-      <c r="AE17" s="110" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF17" s="110" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG17" s="110" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:46" ht="57" customHeight="1">
-      <c r="A18" s="91"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="I18" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="91"/>
-      <c r="T18" s="91"/>
-      <c r="U18" s="91"/>
+        <v>20</v>
+      </c>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="86"/>
+      <c r="N18" s="86"/>
+      <c r="O18" s="86"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="86"/>
+      <c r="R18" s="86"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="86"/>
       <c r="V18" s="43"/>
-      <c r="W18" s="108"/>
-      <c r="X18" s="108"/>
-      <c r="Y18" s="108"/>
-      <c r="Z18" s="108"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="111"/>
-      <c r="AE18" s="111"/>
-      <c r="AF18" s="111"/>
-      <c r="AG18" s="111"/>
-    </row>
-    <row r="19" spans="1:46" s="14" customFormat="1">
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="94"/>
+      <c r="AC18" s="94"/>
+      <c r="AD18" s="102"/>
+      <c r="AE18" s="102"/>
+      <c r="AF18" s="102"/>
+      <c r="AG18" s="102"/>
+    </row>
+    <row r="19" spans="1:46" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>1</v>
       </c>
@@ -2422,133 +2395,133 @@
         <v>21</v>
       </c>
       <c r="V19" s="41"/>
-      <c r="W19" s="109"/>
-      <c r="X19" s="109"/>
-      <c r="Y19" s="109"/>
-      <c r="Z19" s="109"/>
-      <c r="AA19" s="109"/>
-      <c r="AB19" s="119"/>
-      <c r="AC19" s="119"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
+      <c r="W19" s="89"/>
+      <c r="X19" s="89"/>
+      <c r="Y19" s="89"/>
+      <c r="Z19" s="89"/>
+      <c r="AA19" s="89"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="95"/>
+      <c r="AD19" s="103"/>
+      <c r="AE19" s="103"/>
+      <c r="AF19" s="103"/>
+      <c r="AG19" s="103"/>
       <c r="AI19" s="27"/>
       <c r="AM19" s="24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AN19" s="24" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AP19" s="26"/>
       <c r="AQ19" s="26"/>
       <c r="AR19" s="26"/>
     </row>
-    <row r="20" spans="1:46">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q20" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R20" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="M20" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" s="22" t="s">
+      <c r="S20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="T20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q20" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="R20" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="S20" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="T20" s="22" t="s">
-        <v>46</v>
-      </c>
       <c r="U20" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V20" s="44"/>
       <c r="W20" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="X20" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y20" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z20" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA20" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB20" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC20" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD20" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE20" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="X20" s="46" t="s">
+      <c r="AF20" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="Y20" s="46" t="s">
+      <c r="AG20" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="Z20" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="AA20" s="46" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB20" s="47" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC20" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD20" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE20" s="48" t="s">
-        <v>185</v>
-      </c>
-      <c r="AF20" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG20" s="48" t="s">
-        <v>187</v>
-      </c>
       <c r="AI20" s="29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AJ20" s="29" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AK20" s="29">
         <v>1</v>
       </c>
       <c r="AL20" s="28" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AM20" s="30"/>
       <c r="AN20" s="30"/>
@@ -2557,118 +2530,118 @@
       <c r="AQ20" s="31"/>
       <c r="AR20" s="31"/>
     </row>
-    <row r="21" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A21" s="102" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="103"/>
+    <row r="21" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="111"/>
       <c r="C21" s="53"/>
       <c r="D21" s="38"/>
       <c r="E21" s="39"/>
       <c r="F21" s="39"/>
       <c r="G21" s="39" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K21" s="39"/>
       <c r="L21" s="39" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M21" s="39" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N21" s="39" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O21" s="39" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P21" s="39" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q21" s="39"/>
       <c r="R21" s="39" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="S21" s="39"/>
       <c r="T21" s="39" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U21" s="40" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V21" s="49"/>
       <c r="W21" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="X21" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y21" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z21" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA21" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB21" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC21" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD21" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="AE21" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="X21" s="50" t="s">
+      <c r="AF21" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="Y21" s="50" t="s">
+      <c r="AG21" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="Z21" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA21" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB21" s="50" t="s">
-        <v>193</v>
-      </c>
-      <c r="AC21" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="AD21" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE21" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="AF21" s="50" t="s">
-        <v>197</v>
-      </c>
-      <c r="AG21" s="50" t="s">
-        <v>198</v>
-      </c>
       <c r="AI21" s="32" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ21" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK21" s="32">
         <v>1</v>
       </c>
       <c r="AL21" s="32" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AM21" s="32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN21" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AO21" s="32"/>
       <c r="AP21" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ21" s="25" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AR21" s="25">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="15.75" customHeight="1">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2703,42 +2676,42 @@
       <c r="AF22" s="51"/>
       <c r="AG22" s="51"/>
       <c r="AI22" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="AK22" s="24">
         <v>7</v>
       </c>
       <c r="AL22" s="24" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A23" s="95" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="96"/>
-      <c r="L23" s="96"/>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96"/>
-      <c r="Q23" s="96"/>
-      <c r="R23" s="96"/>
-      <c r="S23" s="96"/>
-      <c r="T23" s="96"/>
-      <c r="U23" s="96"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="104" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="105"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
+      <c r="Q23" s="105"/>
+      <c r="R23" s="105"/>
+      <c r="S23" s="105"/>
+      <c r="T23" s="105"/>
+      <c r="U23" s="105"/>
       <c r="V23" s="51"/>
       <c r="W23" s="51"/>
       <c r="X23" s="51"/>
@@ -2752,7 +2725,7 @@
       <c r="AF23" s="51"/>
       <c r="AG23" s="51"/>
     </row>
-    <row r="24" spans="1:46" ht="15.75" customHeight="1">
+    <row r="24" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2787,49 +2760,49 @@
       <c r="AF24" s="52"/>
       <c r="AG24" s="52"/>
     </row>
-    <row r="25" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A25" s="91" t="s">
+    <row r="25" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="86" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="106"/>
+      <c r="D25" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="99"/>
-      <c r="D25" s="91" t="s">
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91" t="s">
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="R25" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="91"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="94" t="s">
+      <c r="S25" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="97" t="s">
+      <c r="T25" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="R25" s="98" t="s">
+      <c r="U25" s="96" t="s">
         <v>11</v>
-      </c>
-      <c r="S25" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="T25" s="98" t="s">
-        <v>13</v>
-      </c>
-      <c r="U25" s="98" t="s">
-        <v>14</v>
       </c>
       <c r="V25" s="52"/>
       <c r="W25" s="52"/>
@@ -2844,48 +2817,48 @@
       <c r="AF25" s="52"/>
       <c r="AG25" s="52"/>
     </row>
-    <row r="26" spans="1:46" ht="15.75">
-      <c r="A26" s="91"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="91" t="s">
+    <row r="26" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="86"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="91" t="s">
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91" t="s">
+      <c r="L26" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="91" t="s">
+      <c r="M26" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="91"/>
-      <c r="J26" s="91"/>
-      <c r="K26" s="94" t="s">
+      <c r="N26" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="L26" s="94" t="s">
+      <c r="O26" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="M26" s="94" t="s">
+      <c r="P26" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="N26" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="O26" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="P26" s="94" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q26" s="97"/>
-      <c r="R26" s="98"/>
-      <c r="S26" s="97"/>
-      <c r="T26" s="98"/>
-      <c r="U26" s="98"/>
+      <c r="Q26" s="109"/>
+      <c r="R26" s="96"/>
+      <c r="S26" s="109"/>
+      <c r="T26" s="96"/>
+      <c r="U26" s="96"/>
       <c r="V26" s="52"/>
       <c r="W26" s="52"/>
       <c r="X26" s="52"/>
@@ -2899,34 +2872,34 @@
       <c r="AF26" s="52"/>
       <c r="AG26" s="52"/>
     </row>
-    <row r="27" spans="1:46" ht="48" customHeight="1">
-      <c r="A27" s="91"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
+    <row r="27" spans="1:46" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="86"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="86"/>
       <c r="H27" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="91"/>
-      <c r="T27" s="91"/>
-      <c r="U27" s="91"/>
+        <v>20</v>
+      </c>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="86"/>
+      <c r="N27" s="86"/>
+      <c r="O27" s="86"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="86"/>
       <c r="V27" s="52"/>
       <c r="W27" s="52"/>
       <c r="X27" s="52"/>
@@ -2940,7 +2913,7 @@
       <c r="AF27" s="52"/>
       <c r="AG27" s="52"/>
     </row>
-    <row r="28" spans="1:46" ht="15.75">
+    <row r="28" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>1</v>
       </c>
@@ -3015,61 +2988,61 @@
       <c r="AF28" s="52"/>
       <c r="AG28" s="52"/>
     </row>
-    <row r="29" spans="1:46" ht="15.75">
+    <row r="29" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="22" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="N29" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="O29" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="P29" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="R29" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="S29" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="T29" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="U29" s="23" t="s">
         <v>78</v>
-      </c>
-      <c r="N29" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="O29" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="P29" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q29" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="R29" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="S29" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="T29" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="U29" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="V29" s="52"/>
       <c r="W29" s="52"/>
@@ -3084,16 +3057,16 @@
       <c r="AF29" s="52"/>
       <c r="AG29" s="52"/>
       <c r="AI29" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ29" s="34" t="s">
         <v>62</v>
-      </c>
-      <c r="AJ29" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="AK29" s="29">
         <v>1</v>
       </c>
       <c r="AL29" s="35" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AM29" s="30"/>
       <c r="AN29" s="30"/>
@@ -3102,53 +3075,53 @@
       <c r="AQ29" s="31"/>
       <c r="AR29" s="31"/>
     </row>
-    <row r="30" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A30" s="92" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="93"/>
+    <row r="30" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="113"/>
       <c r="C30" s="54"/>
       <c r="D30" s="13"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="Q30" s="11"/>
       <c r="R30" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="S30" s="11"/>
       <c r="T30" s="11" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="V30" s="52"/>
       <c r="W30" s="52"/>
@@ -3163,41 +3136,41 @@
       <c r="AF30" s="52"/>
       <c r="AG30" s="52"/>
       <c r="AI30" s="32" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ30" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK30" s="32">
         <v>1</v>
       </c>
       <c r="AL30" s="36" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AM30" s="32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN30" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AO30" s="32"/>
       <c r="AP30" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ30" s="37" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AR30" s="25">
         <v>0</v>
       </c>
       <c r="AS30" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT30" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="AT30" s="33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="15.75" customHeight="1">
+    </row>
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -3232,42 +3205,42 @@
       <c r="AF31" s="52"/>
       <c r="AG31" s="52"/>
       <c r="AI31" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ31" s="33" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AK31" s="24">
         <v>7</v>
       </c>
       <c r="AL31" s="24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A32" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="96"/>
-      <c r="U32" s="96"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="105"/>
+      <c r="O32" s="105"/>
+      <c r="P32" s="105"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="105"/>
+      <c r="S32" s="105"/>
+      <c r="T32" s="105"/>
+      <c r="U32" s="105"/>
       <c r="AI32" s="14"/>
       <c r="AJ32" s="14"/>
       <c r="AK32" s="14"/>
@@ -3281,7 +3254,7 @@
       <c r="AS32" s="14"/>
       <c r="AT32" s="14"/>
     </row>
-    <row r="33" spans="1:46" ht="15.75" customHeight="1">
+    <row r="33" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3316,49 +3289,49 @@
       <c r="AS33" s="14"/>
       <c r="AT33" s="14"/>
     </row>
-    <row r="34" spans="1:46" ht="15" customHeight="1">
-      <c r="A34" s="91" t="s">
+    <row r="34" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="86" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="106"/>
+      <c r="D34" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="99"/>
-      <c r="D34" s="91" t="s">
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91" t="s">
+      <c r="L34" s="86"/>
+      <c r="M34" s="86"/>
+      <c r="N34" s="86"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="R34" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="G34" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="91"/>
-      <c r="K34" s="94" t="s">
+      <c r="S34" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="L34" s="91"/>
-      <c r="M34" s="91"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="91"/>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="97" t="s">
+      <c r="T34" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="R34" s="98" t="s">
+      <c r="U34" s="96" t="s">
         <v>11</v>
-      </c>
-      <c r="S34" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="T34" s="98" t="s">
-        <v>13</v>
-      </c>
-      <c r="U34" s="98" t="s">
-        <v>14</v>
       </c>
       <c r="AI34" s="14"/>
       <c r="AJ34" s="14"/>
@@ -3373,48 +3346,48 @@
       <c r="AS34" s="14"/>
       <c r="AT34" s="14"/>
     </row>
-    <row r="35" spans="1:46">
-      <c r="A35" s="91"/>
-      <c r="B35" s="91"/>
-      <c r="C35" s="100"/>
-      <c r="D35" s="91" t="s">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A35" s="86"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="86"/>
+      <c r="G35" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="91" t="s">
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="91"/>
-      <c r="G35" s="91" t="s">
+      <c r="L35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="91" t="s">
+      <c r="M35" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="91"/>
-      <c r="J35" s="91"/>
-      <c r="K35" s="94" t="s">
+      <c r="N35" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="L35" s="94" t="s">
+      <c r="O35" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="M35" s="94" t="s">
+      <c r="P35" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="N35" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="O35" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="P35" s="94" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
-      <c r="S35" s="97"/>
-      <c r="T35" s="98"/>
-      <c r="U35" s="98"/>
+      <c r="Q35" s="109"/>
+      <c r="R35" s="96"/>
+      <c r="S35" s="109"/>
+      <c r="T35" s="96"/>
+      <c r="U35" s="96"/>
       <c r="AI35" s="14"/>
       <c r="AJ35" s="14"/>
       <c r="AK35" s="14"/>
@@ -3428,34 +3401,34 @@
       <c r="AS35" s="14"/>
       <c r="AT35" s="14"/>
     </row>
-    <row r="36" spans="1:46" ht="48" customHeight="1">
-      <c r="A36" s="91"/>
-      <c r="B36" s="91"/>
-      <c r="C36" s="101"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="91"/>
-      <c r="G36" s="91"/>
+    <row r="36" spans="1:46" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="86"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
       <c r="H36" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="91"/>
-      <c r="L36" s="91"/>
-      <c r="M36" s="91"/>
-      <c r="N36" s="91"/>
-      <c r="O36" s="91"/>
-      <c r="P36" s="91"/>
-      <c r="Q36" s="91"/>
-      <c r="R36" s="91"/>
-      <c r="S36" s="91"/>
-      <c r="T36" s="91"/>
-      <c r="U36" s="91"/>
+        <v>20</v>
+      </c>
+      <c r="K36" s="86"/>
+      <c r="L36" s="86"/>
+      <c r="M36" s="86"/>
+      <c r="N36" s="86"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="86"/>
+      <c r="Q36" s="86"/>
+      <c r="R36" s="86"/>
+      <c r="S36" s="86"/>
+      <c r="T36" s="86"/>
+      <c r="U36" s="86"/>
       <c r="AI36" s="14"/>
       <c r="AJ36" s="14"/>
       <c r="AK36" s="14"/>
@@ -3469,7 +3442,7 @@
       <c r="AS36" s="14"/>
       <c r="AT36" s="14"/>
     </row>
-    <row r="37" spans="1:46">
+    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
         <v>1</v>
       </c>
@@ -3544,73 +3517,73 @@
       <c r="AS37" s="14"/>
       <c r="AT37" s="14"/>
     </row>
-    <row r="38" spans="1:46">
+    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="22" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="M38" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="N38" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="O38" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="P38" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q38" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="R38" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="S38" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="T38" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="U38" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="N38" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="O38" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="P38" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q38" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="R38" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="S38" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="T38" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="U38" s="23" t="s">
-        <v>123</v>
-      </c>
       <c r="AI38" s="29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AJ38" s="34" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AK38" s="29">
         <v>1</v>
       </c>
       <c r="AL38" s="35" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AM38" s="30"/>
       <c r="AN38" s="30"/>
@@ -3621,90 +3594,90 @@
       <c r="AS38" s="14"/>
       <c r="AT38" s="14"/>
     </row>
-    <row r="39" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A39" s="92" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="93"/>
+    <row r="39" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="113"/>
       <c r="C39" s="54"/>
       <c r="D39" s="13"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K39" s="11"/>
       <c r="L39" s="11" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="P39" s="11" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="Q39" s="11"/>
       <c r="R39" s="11" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="S39" s="11"/>
       <c r="T39" s="11" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="U39" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="AI39" s="32" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ39" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK39" s="32">
         <v>1</v>
       </c>
       <c r="AL39" s="36" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AM39" s="32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN39" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AO39" s="32"/>
       <c r="AP39" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ39" s="37" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AR39" s="25">
         <v>0</v>
       </c>
       <c r="AS39" s="24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AT39" s="33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="15.75" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -3727,42 +3700,42 @@
       <c r="T40" s="20"/>
       <c r="U40" s="21"/>
       <c r="AI40" s="24" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ40" s="33" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AK40" s="24">
         <v>7</v>
       </c>
       <c r="AL40" s="24" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A41" s="95" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
-      <c r="N41" s="96"/>
-      <c r="O41" s="96"/>
-      <c r="P41" s="96"/>
-      <c r="Q41" s="96"/>
-      <c r="R41" s="96"/>
-      <c r="S41" s="96"/>
-      <c r="T41" s="96"/>
-      <c r="U41" s="96"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="105"/>
+      <c r="N41" s="105"/>
+      <c r="O41" s="105"/>
+      <c r="P41" s="105"/>
+      <c r="Q41" s="105"/>
+      <c r="R41" s="105"/>
+      <c r="S41" s="105"/>
+      <c r="T41" s="105"/>
+      <c r="U41" s="105"/>
       <c r="AI41" s="14"/>
       <c r="AJ41" s="14"/>
       <c r="AK41" s="14"/>
@@ -3776,7 +3749,7 @@
       <c r="AS41" s="14"/>
       <c r="AT41" s="14"/>
     </row>
-    <row r="42" spans="1:46" ht="15.75" customHeight="1">
+    <row r="42" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3811,49 +3784,49 @@
       <c r="AS42" s="14"/>
       <c r="AT42" s="14"/>
     </row>
-    <row r="43" spans="1:46" ht="15" customHeight="1">
-      <c r="A43" s="91" t="s">
+    <row r="43" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="86" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="106"/>
+      <c r="D43" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="86"/>
+      <c r="F43" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="91" t="s">
+      <c r="H43" s="86"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
+      <c r="K43" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="91"/>
-      <c r="F43" s="91" t="s">
+      <c r="L43" s="86"/>
+      <c r="M43" s="86"/>
+      <c r="N43" s="86"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="R43" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" s="91"/>
-      <c r="I43" s="91"/>
-      <c r="J43" s="91"/>
-      <c r="K43" s="94" t="s">
+      <c r="S43" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="L43" s="91"/>
-      <c r="M43" s="91"/>
-      <c r="N43" s="91"/>
-      <c r="O43" s="91"/>
-      <c r="P43" s="91"/>
-      <c r="Q43" s="97" t="s">
+      <c r="T43" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="R43" s="98" t="s">
+      <c r="U43" s="96" t="s">
         <v>11</v>
-      </c>
-      <c r="S43" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="T43" s="98" t="s">
-        <v>13</v>
-      </c>
-      <c r="U43" s="98" t="s">
-        <v>14</v>
       </c>
       <c r="AI43" s="14"/>
       <c r="AJ43" s="14"/>
@@ -3868,48 +3841,48 @@
       <c r="AS43" s="14"/>
       <c r="AT43" s="14"/>
     </row>
-    <row r="44" spans="1:46">
-      <c r="A44" s="91"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="100"/>
-      <c r="D44" s="91" t="s">
+    <row r="44" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A44" s="86"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="107"/>
+      <c r="D44" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="86"/>
+      <c r="G44" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="91" t="s">
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="91"/>
-      <c r="G44" s="91" t="s">
+      <c r="L44" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H44" s="91" t="s">
+      <c r="M44" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="91"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="94" t="s">
+      <c r="N44" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="L44" s="94" t="s">
+      <c r="O44" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="M44" s="94" t="s">
+      <c r="P44" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="N44" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="O44" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="P44" s="94" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q44" s="97"/>
-      <c r="R44" s="98"/>
-      <c r="S44" s="97"/>
-      <c r="T44" s="98"/>
-      <c r="U44" s="98"/>
+      <c r="Q44" s="109"/>
+      <c r="R44" s="96"/>
+      <c r="S44" s="109"/>
+      <c r="T44" s="96"/>
+      <c r="U44" s="96"/>
       <c r="AI44" s="14"/>
       <c r="AJ44" s="14"/>
       <c r="AK44" s="14"/>
@@ -3923,34 +3896,34 @@
       <c r="AS44" s="14"/>
       <c r="AT44" s="14"/>
     </row>
-    <row r="45" spans="1:46" ht="48" customHeight="1">
-      <c r="A45" s="91"/>
-      <c r="B45" s="91"/>
-      <c r="C45" s="101"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
-      <c r="F45" s="91"/>
-      <c r="G45" s="91"/>
+    <row r="45" spans="1:46" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="86"/>
+      <c r="B45" s="86"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="86"/>
+      <c r="E45" s="86"/>
+      <c r="F45" s="86"/>
+      <c r="G45" s="86"/>
       <c r="H45" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K45" s="91"/>
-      <c r="L45" s="91"/>
-      <c r="M45" s="91"/>
-      <c r="N45" s="91"/>
-      <c r="O45" s="91"/>
-      <c r="P45" s="91"/>
-      <c r="Q45" s="91"/>
-      <c r="R45" s="91"/>
-      <c r="S45" s="91"/>
-      <c r="T45" s="91"/>
-      <c r="U45" s="91"/>
+        <v>20</v>
+      </c>
+      <c r="K45" s="86"/>
+      <c r="L45" s="86"/>
+      <c r="M45" s="86"/>
+      <c r="N45" s="86"/>
+      <c r="O45" s="86"/>
+      <c r="P45" s="86"/>
+      <c r="Q45" s="86"/>
+      <c r="R45" s="86"/>
+      <c r="S45" s="86"/>
+      <c r="T45" s="86"/>
+      <c r="U45" s="86"/>
       <c r="AI45" s="14"/>
       <c r="AJ45" s="14"/>
       <c r="AK45" s="14"/>
@@ -3964,7 +3937,7 @@
       <c r="AS45" s="14"/>
       <c r="AT45" s="14"/>
     </row>
-    <row r="46" spans="1:46">
+    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>1</v>
       </c>
@@ -4039,73 +4012,73 @@
       <c r="AS46" s="14"/>
       <c r="AT46" s="14"/>
     </row>
-    <row r="47" spans="1:46">
+    <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="22" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="M47" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="N47" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="O47" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="P47" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q47" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="R47" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="S47" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="T47" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="M47" s="22" t="s">
+      <c r="U47" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="N47" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="O47" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="P47" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q47" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="R47" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="S47" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="T47" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="U47" s="23" t="s">
-        <v>150</v>
-      </c>
       <c r="AI47" s="29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AJ47" s="34" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AK47" s="29">
         <v>1</v>
       </c>
       <c r="AL47" s="35" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AM47" s="30"/>
       <c r="AN47" s="30"/>
@@ -4116,90 +4089,90 @@
       <c r="AS47" s="14"/>
       <c r="AT47" s="14"/>
     </row>
-    <row r="48" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A48" s="92" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" s="93"/>
+    <row r="48" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="113"/>
       <c r="C48" s="54"/>
       <c r="D48" s="13"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="11" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="P48" s="11" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q48" s="11"/>
       <c r="R48" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="S48" s="11"/>
       <c r="T48" s="11" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AI48" s="32" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AJ48" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK48" s="32">
         <v>1</v>
       </c>
       <c r="AL48" s="36" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AM48" s="32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AN48" s="32" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AO48" s="32"/>
       <c r="AP48" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ48" s="37" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AR48" s="25">
         <v>0</v>
       </c>
       <c r="AS48" s="24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AT48" s="33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:61" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -4221,16 +4194,16 @@
       <c r="U49" s="5"/>
       <c r="AH49" s="26"/>
       <c r="AI49" s="26" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ49" s="55" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="AK49" s="26">
         <v>14</v>
       </c>
       <c r="AL49" s="26" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AM49" s="26"/>
       <c r="AN49" s="26"/>
@@ -4256,7 +4229,7 @@
       <c r="BH49" s="26"/>
       <c r="BI49" s="26"/>
     </row>
-    <row r="50" spans="1:61" s="26" customFormat="1" ht="18.75">
+    <row r="50" spans="1:61" s="26" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B50" s="72"/>
       <c r="C50" s="72"/>
       <c r="D50" s="72"/>
@@ -4278,7 +4251,7 @@
       <c r="T50" s="72"/>
       <c r="U50" s="72"/>
     </row>
-    <row r="51" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
+    <row r="51" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="73"/>
       <c r="B51" s="74"/>
       <c r="C51" s="74"/>
@@ -4301,11 +4274,11 @@
       <c r="T51" s="74"/>
       <c r="U51" s="75"/>
     </row>
-    <row r="52" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A52" s="73"/>
-      <c r="B52" s="77" t="s">
-        <v>30</v>
-      </c>
+    <row r="52" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="B52" s="77"/>
       <c r="C52" s="77"/>
       <c r="D52" s="77"/>
       <c r="E52" s="77"/>
@@ -4315,10 +4288,10 @@
       <c r="I52" s="77"/>
       <c r="J52" s="77"/>
       <c r="K52" s="77"/>
-      <c r="L52" s="77" t="s">
-        <v>32</v>
-      </c>
-      <c r="M52" s="77"/>
+      <c r="L52" s="77"/>
+      <c r="M52" s="77" t="s">
+        <v>201</v>
+      </c>
       <c r="N52" s="78"/>
       <c r="O52" s="78"/>
       <c r="P52" s="79"/>
@@ -4328,11 +4301,9 @@
       <c r="T52" s="78"/>
       <c r="U52" s="78"/>
     </row>
-    <row r="53" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A53" s="73"/>
-      <c r="B53" s="77" t="s">
-        <v>31</v>
-      </c>
+    <row r="53" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="74"/>
+      <c r="B53" s="77"/>
       <c r="C53" s="77"/>
       <c r="D53" s="77"/>
       <c r="E53" s="77"/>
@@ -4342,26 +4313,24 @@
       <c r="I53" s="77"/>
       <c r="J53" s="77"/>
       <c r="K53" s="77"/>
-      <c r="L53" s="80" t="s">
-        <v>33</v>
-      </c>
-      <c r="M53" s="80"/>
+      <c r="L53" s="80"/>
+      <c r="M53" s="80" t="s">
+        <v>202</v>
+      </c>
       <c r="N53" s="80"/>
       <c r="O53" s="80"/>
       <c r="P53" s="80"/>
       <c r="Q53" s="77" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R53" s="74"/>
       <c r="S53" s="74"/>
       <c r="T53" s="80"/>
       <c r="U53" s="77"/>
     </row>
-    <row r="54" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A54" s="73"/>
-      <c r="B54" s="77" t="s">
-        <v>3</v>
-      </c>
+    <row r="54" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="74"/>
+      <c r="B54" s="77"/>
       <c r="C54" s="77"/>
       <c r="D54" s="77"/>
       <c r="E54" s="77"/>
@@ -4382,8 +4351,10 @@
       <c r="T54" s="77"/>
       <c r="U54" s="77"/>
     </row>
-    <row r="55" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A55" s="73"/>
+    <row r="55" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="74" t="s">
+        <v>204</v>
+      </c>
       <c r="B55" s="77"/>
       <c r="C55" s="77"/>
       <c r="D55" s="77"/>
@@ -4405,11 +4376,9 @@
       <c r="T55" s="77"/>
       <c r="U55" s="77"/>
     </row>
-    <row r="56" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A56" s="73"/>
-      <c r="B56" s="77" t="s">
-        <v>34</v>
-      </c>
+    <row r="56" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="74"/>
+      <c r="B56" s="77"/>
       <c r="C56" s="77"/>
       <c r="D56" s="77"/>
       <c r="E56" s="77"/>
@@ -4419,23 +4388,25 @@
       <c r="I56" s="77"/>
       <c r="J56" s="77"/>
       <c r="K56" s="77"/>
-      <c r="L56" s="80" t="s">
-        <v>206</v>
-      </c>
-      <c r="M56" s="80"/>
+      <c r="L56" s="80"/>
+      <c r="M56" s="80" t="s">
+        <v>205</v>
+      </c>
       <c r="N56" s="80"/>
       <c r="O56" s="80"/>
       <c r="P56" s="80"/>
       <c r="Q56" s="78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R56" s="74"/>
       <c r="S56" s="74"/>
       <c r="T56" s="77"/>
       <c r="U56" s="77"/>
     </row>
-    <row r="57" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A57" s="73"/>
+    <row r="57" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="74" t="s">
+        <v>27</v>
+      </c>
       <c r="B57" s="77"/>
       <c r="C57" s="77"/>
       <c r="D57" s="77"/>
@@ -4457,11 +4428,9 @@
       <c r="T57" s="77"/>
       <c r="U57" s="77"/>
     </row>
-    <row r="58" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A58" s="73"/>
-      <c r="B58" s="77" t="s">
-        <v>35</v>
-      </c>
+    <row r="58" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="74"/>
+      <c r="B58" s="77"/>
       <c r="C58" s="77"/>
       <c r="D58" s="77"/>
       <c r="E58" s="77"/>
@@ -4472,18 +4441,24 @@
       <c r="J58" s="77"/>
       <c r="K58" s="77"/>
       <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
+      <c r="M58" s="65" t="s">
+        <v>197</v>
+      </c>
       <c r="N58" s="65"/>
       <c r="O58" s="65"/>
       <c r="P58" s="65"/>
-      <c r="Q58" s="77"/>
+      <c r="Q58" s="77" t="s">
+        <v>207</v>
+      </c>
       <c r="R58" s="74"/>
       <c r="S58" s="74"/>
       <c r="T58" s="65"/>
       <c r="U58" s="83"/>
     </row>
-    <row r="59" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A59" s="73"/>
+    <row r="59" spans="1:61" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="74" t="s">
+        <v>208</v>
+      </c>
       <c r="B59" s="77"/>
       <c r="C59" s="77"/>
       <c r="D59" s="77"/>
@@ -4505,10 +4480,8 @@
       <c r="T59" s="65"/>
       <c r="U59" s="77"/>
     </row>
-    <row r="60" spans="1:61" s="31" customFormat="1" ht="18.75">
-      <c r="B60" s="77" t="s">
-        <v>214</v>
-      </c>
+    <row r="60" spans="1:61" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B60" s="77"/>
       <c r="C60" s="77"/>
       <c r="D60" s="77"/>
       <c r="E60" s="77"/>
@@ -4518,22 +4491,18 @@
       <c r="I60" s="77"/>
       <c r="J60" s="77"/>
       <c r="K60" s="77"/>
-      <c r="L60" s="84" t="s">
-        <v>215</v>
-      </c>
+      <c r="L60" s="84"/>
       <c r="M60" s="84"/>
       <c r="N60" s="84"/>
       <c r="O60" s="77"/>
       <c r="P60" s="77"/>
-      <c r="Q60" s="84" t="s">
-        <v>216</v>
-      </c>
+      <c r="Q60" s="84"/>
       <c r="R60" s="74"/>
       <c r="S60" s="74"/>
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
     </row>
-    <row r="61" spans="1:61" s="31" customFormat="1" ht="18.75">
+    <row r="61" spans="1:61" s="31" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
       <c r="D61" s="74"/>
@@ -4555,17 +4524,17 @@
       <c r="T61" s="74"/>
       <c r="U61" s="74"/>
     </row>
-    <row r="62" spans="1:61" s="28" customFormat="1">
+    <row r="62" spans="1:61" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AH62" s="31"/>
       <c r="AI62" s="31"/>
       <c r="AJ62" s="31"/>
       <c r="AK62" s="31"/>
       <c r="AL62" s="31"/>
       <c r="AM62" s="31" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AN62" s="56" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="AO62" s="31"/>
       <c r="AP62" s="31"/>
@@ -4589,10 +4558,10 @@
       <c r="BH62" s="31"/>
       <c r="BI62" s="31"/>
     </row>
-    <row r="63" spans="1:61" s="14" customFormat="1">
+    <row r="63" spans="1:61" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AH63" s="26"/>
       <c r="AI63" s="57" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="AJ63" s="26"/>
       <c r="AK63" s="26"/>
@@ -4624,49 +4593,52 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="113">
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="W16:W19"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AB16:AB19"/>
-    <mergeCell ref="AC16:AC19"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="U16:U18"/>
-    <mergeCell ref="AD16:AE16"/>
-    <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="X17:X19"/>
-    <mergeCell ref="Y17:Y19"/>
-    <mergeCell ref="Z17:Z19"/>
-    <mergeCell ref="AA17:AA19"/>
-    <mergeCell ref="AD17:AD19"/>
-    <mergeCell ref="AE17:AE19"/>
-    <mergeCell ref="AF17:AF19"/>
-    <mergeCell ref="AG17:AG19"/>
-    <mergeCell ref="A23:U23"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="K16:P16"/>
-    <mergeCell ref="Q16:Q18"/>
-    <mergeCell ref="R16:R18"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="T16:T18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="M35:M36"/>
-    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="A15:U15"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="P44:P45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="O44:O45"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:U41"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="K43:P43"/>
+    <mergeCell ref="Q43:Q45"/>
+    <mergeCell ref="R43:R45"/>
+    <mergeCell ref="S43:S45"/>
+    <mergeCell ref="T43:T45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:U32"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="Q34:Q36"/>
+    <mergeCell ref="R34:R36"/>
+    <mergeCell ref="S34:S36"/>
+    <mergeCell ref="T34:T36"/>
+    <mergeCell ref="U34:U36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L35:L36"/>
     <mergeCell ref="C43:C45"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A25:A27"/>
@@ -4691,52 +4663,49 @@
     <mergeCell ref="T25:T27"/>
     <mergeCell ref="U43:U45"/>
     <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:U32"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="Q34:Q36"/>
-    <mergeCell ref="R34:R36"/>
-    <mergeCell ref="S34:S36"/>
-    <mergeCell ref="T34:T36"/>
-    <mergeCell ref="U34:U36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L35:L36"/>
-    <mergeCell ref="A13:U13"/>
-    <mergeCell ref="A15:U15"/>
-    <mergeCell ref="A14:U14"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="P44:P45"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="N44:N45"/>
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:U41"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="K43:P43"/>
-    <mergeCell ref="Q43:Q45"/>
-    <mergeCell ref="R43:R45"/>
-    <mergeCell ref="S43:S45"/>
-    <mergeCell ref="T43:T45"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="AD16:AE16"/>
+    <mergeCell ref="AF16:AG16"/>
+    <mergeCell ref="X17:X19"/>
+    <mergeCell ref="Y17:Y19"/>
+    <mergeCell ref="Z17:Z19"/>
+    <mergeCell ref="AA17:AA19"/>
+    <mergeCell ref="AD17:AD19"/>
+    <mergeCell ref="AE17:AE19"/>
+    <mergeCell ref="AF17:AF19"/>
+    <mergeCell ref="AG17:AG19"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="W16:W19"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AB16:AB19"/>
+    <mergeCell ref="AC16:AC19"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="U16:U18"/>
+    <mergeCell ref="A23:U23"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="K16:P16"/>
+    <mergeCell ref="Q16:Q18"/>
+    <mergeCell ref="R16:R18"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="T16:T18"/>
+    <mergeCell ref="D17:D18"/>
   </mergeCells>
   <pageMargins left="0.70866141732282995" right="0.70866141732282995" top="0.74803149606299002" bottom="0.74803149606299002" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup scale="28" fitToHeight="500" orientation="portrait" r:id="rId1"/>
